--- a/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22327</t>
+          <t>22183</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36818</t>
+          <t>36681</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>21,08%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32042</t>
+          <t>31215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48714</t>
+          <t>48273</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,18%</t>
+          <t>40,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58541</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81146</t>
+          <t>80411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,31%</t>
+          <t>35,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>68391</t>
+          <t>68528</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82882</t>
+          <t>83026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,0%</t>
+          <t>65,14%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,92%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69575</t>
+          <t>70016</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86247</t>
+          <t>87074</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>58,82%</t>
+          <t>59,19%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>142353</t>
+          <t>143088</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>164958</t>
+          <t>165838</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30402</t>
+          <t>30537</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46995</t>
+          <t>46393</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>24,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,61%</t>
+          <t>37,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42717</t>
+          <t>42773</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60718</t>
+          <t>60345</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>42,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78087</t>
+          <t>78600</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>100507</t>
+          <t>102179</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>38,46%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>77970</t>
+          <t>78572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>94563</t>
+          <t>94428</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,39%</t>
+          <t>62,88%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>80024</t>
+          <t>80397</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>98025</t>
+          <t>97969</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165200</t>
+          <t>163528</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187620</t>
+          <t>187107</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>61,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,42%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35054</t>
+          <t>35328</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>49575</t>
+          <t>51099</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39980</t>
+          <t>40240</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>56231</t>
+          <t>55911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>49,95%</t>
+          <t>49,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>78909</t>
+          <t>79312</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102015</t>
+          <t>101600</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>58273</t>
+          <t>56749</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>72794</t>
+          <t>72520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>67,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>56342</t>
+          <t>56662</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>72333</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>50,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118405</t>
+          <t>118820</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>141511</t>
+          <t>141108</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45733</t>
+          <t>45141</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66020</t>
+          <t>66415</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48762</t>
+          <t>48677</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>68061</t>
+          <t>67939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>97239</t>
+          <t>99006</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126625</t>
+          <t>126188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>30,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,15%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99316</t>
+          <t>98921</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119603</t>
+          <t>120195</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>88885</t>
+          <t>89007</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>108184</t>
+          <t>108269</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,63%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195657</t>
+          <t>196094</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>225043</t>
+          <t>223276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,71%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,83%</t>
+          <t>69,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>149513</t>
+          <t>148119</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>182265</t>
+          <t>182107</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>179082</t>
+          <t>179464</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>213526</t>
+          <t>214454</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>338020</t>
+          <t>337770</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>386435</t>
+          <t>388260</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,45%</t>
+          <t>37,63%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>321094</t>
+          <t>321252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>353846</t>
+          <t>355240</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,3%</t>
+          <t>70,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>315023</t>
+          <t>314095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>349467</t>
+          <t>349085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,43%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>645473</t>
+          <t>643648</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>693888</t>
+          <t>694138</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,55%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,24%</t>
+          <t>67,27%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27644</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43336</t>
+          <t>43409</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30857</t>
+          <t>31748</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48647</t>
+          <t>48999</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,24%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64208</t>
+          <t>64101</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86363</t>
+          <t>86393</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>41,21%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>53793</t>
+          <t>53720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69485</t>
+          <t>70449</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>55,38%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63854</t>
+          <t>63502</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81644</t>
+          <t>80753</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>71,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123266</t>
+          <t>123236</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145421</t>
+          <t>145528</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,42%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>39018</t>
+          <t>39079</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>56635</t>
+          <t>56847</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>44,07%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49982</t>
+          <t>50866</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>70618</t>
+          <t>70682</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,34%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94544</t>
+          <t>95246</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121478</t>
+          <t>120370</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,84%</t>
+          <t>42,45%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>72348</t>
+          <t>72136</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>89965</t>
+          <t>89904</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,09%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>83938</t>
+          <t>83874</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>104574</t>
+          <t>103690</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,66%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>162061</t>
+          <t>163169</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188995</t>
+          <t>188293</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>66,41%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26672</t>
+          <t>27155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>42309</t>
+          <t>41943</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>40,35%</t>
+          <t>40,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31599</t>
+          <t>32396</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48392</t>
+          <t>49012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>62929</t>
+          <t>63120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>84960</t>
+          <t>85201</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,33%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>62542</t>
+          <t>62908</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78179</t>
+          <t>77696</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68392</t>
+          <t>67772</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>85185</t>
+          <t>84388</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136674</t>
+          <t>136433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158705</t>
+          <t>158514</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,52%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43504</t>
+          <t>43786</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63886</t>
+          <t>64264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,8%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>39930</t>
+          <t>38758</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>58357</t>
+          <t>59118</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88593</t>
+          <t>88594</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>115647</t>
+          <t>116080</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3799,7 +3799,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>38,57%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82116</t>
+          <t>81738</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102498</t>
+          <t>102216</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>70,2%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96584</t>
+          <t>95823</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>116183</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>185296</t>
+          <t>184863</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212350</t>
+          <t>212349</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>153090</t>
+          <t>153097</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>187837</t>
+          <t>186219</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4072,7 +4072,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>172586</t>
+          <t>172497</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>208284</t>
+          <t>208367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,03%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,66%</t>
+          <t>38,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333641</t>
+          <t>333254</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>385221</t>
+          <t>384731</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>37,88%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>289128</t>
+          <t>290746</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>323875</t>
+          <t>323868</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,7 +4180,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>330497</t>
+          <t>330414</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>366195</t>
+          <t>366284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,34%</t>
+          <t>61,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,97%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>630525</t>
+          <t>631015</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682105</t>
+          <t>682492</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,15%</t>
+          <t>67,19%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22175</t>
+          <t>22618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37375</t>
+          <t>37716</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23401</t>
+          <t>24336</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40107</t>
+          <t>40883</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>39,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51208</t>
+          <t>50057</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72975</t>
+          <t>71730</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>36,83%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52710</t>
+          <t>52369</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>67910</t>
+          <t>67467</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>64567</t>
+          <t>63791</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>80338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>121784</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>143551</t>
+          <t>144702</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,71%</t>
+          <t>74,3%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42742</t>
+          <t>43190</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60667</t>
+          <t>60729</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,93%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>51717</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72832</t>
+          <t>72240</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100286</t>
+          <t>99422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>126408</t>
+          <t>125874</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>38,47%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>91260</t>
+          <t>91198</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109185</t>
+          <t>108737</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>60,07%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>71,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>102471</t>
+          <t>103063</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>123463</t>
+          <t>123586</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>200822</t>
+          <t>201356</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>226944</t>
+          <t>227808</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>69,62%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>26904</t>
+          <t>26917</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41883</t>
+          <t>41561</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36903</t>
+          <t>36532</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54422</t>
+          <t>54500</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,97%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68262</t>
+          <t>68521</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92049</t>
+          <t>92144</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>36,95%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74669</t>
+          <t>74991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89648</t>
+          <t>89635</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78425</t>
+          <t>78347</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95944</t>
+          <t>96315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,03%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,22%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157350</t>
+          <t>157255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>181137</t>
+          <t>180878</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,53%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53763</t>
+          <t>53018</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>74796</t>
+          <t>74548</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,83%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>42081</t>
+          <t>42236</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61717</t>
+          <t>61613</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,6%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>38,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101219</t>
+          <t>100302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129351</t>
+          <t>129361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,7 +5741,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92031</t>
+          <t>92279</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113064</t>
+          <t>113809</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>96491</t>
+          <t>96595</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>116127</t>
+          <t>115972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195684</t>
+          <t>195674</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223816</t>
+          <t>224733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5859,7 +5859,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>69,14%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163082</t>
+          <t>162427</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>198848</t>
+          <t>199215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>31,04%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>173316</t>
+          <t>169476</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>207870</t>
+          <t>207926</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,35%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,4%</t>
+          <t>36,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>342393</t>
+          <t>346326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>393868</t>
+          <t>396908</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,92%</t>
+          <t>36,2%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>326542</t>
+          <t>326175</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>362308</t>
+          <t>362963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,96%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>363163</t>
+          <t>363107</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>397717</t>
+          <t>401557</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,6%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>702555</t>
+          <t>699515</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>754030</t>
+          <t>750097</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>63,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,41%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>82065</t>
+          <t>82328</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>96838</t>
+          <t>97064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>70,2%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>82,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72583</t>
+          <t>72433</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109058</t>
+          <t>109469</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>51,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,67%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>160056</t>
+          <t>158766</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>200802</t>
+          <t>201845</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20442</t>
+          <t>20216</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35215</t>
+          <t>34952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,43%</t>
+          <t>17,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31354</t>
+          <t>30943</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67829</t>
+          <t>67979</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,31%</t>
+          <t>48,41%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56891</t>
+          <t>55848</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>97637</t>
+          <t>98927</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>38,39%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123606</t>
+          <t>123733</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>149885</t>
+          <t>150249</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>64,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>173820</t>
+          <t>174801</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203007</t>
+          <t>203275</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>308843</t>
+          <t>306851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>348504</t>
+          <t>347958</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,1%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>40627</t>
+          <t>40263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>66906</t>
+          <t>66779</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>52028</t>
+          <t>51760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81215</t>
+          <t>80234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97044</t>
+          <t>97590</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>136705</t>
+          <t>138697</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,13%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>142691</t>
+          <t>141329</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>169159</t>
+          <t>168869</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,94%</t>
+          <t>74,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>88,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131998</t>
+          <t>131912</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153668</t>
+          <t>153470</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,19%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>282198</t>
+          <t>281989</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318002</t>
+          <t>318044</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,65%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>21242</t>
+          <t>21532</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>47710</t>
+          <t>49072</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31618</t>
+          <t>31816</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53288</t>
+          <t>53374</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,81%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57685</t>
+          <t>57643</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93489</t>
+          <t>93698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>24,94%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>125129</t>
+          <t>125229</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>142927</t>
+          <t>143317</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>137473</t>
+          <t>136392</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>156234</t>
+          <t>155306</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268317</t>
+          <t>268904</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>294115</t>
+          <t>293381</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,01%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>25035</t>
+          <t>24645</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42833</t>
+          <t>42733</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25004</t>
+          <t>25932</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43765</t>
+          <t>44846</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55086</t>
+          <t>55820</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80884</t>
+          <t>80297</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>495054</t>
+          <t>494793</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>541281</t>
+          <t>542431</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,32%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,25%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>543841</t>
+          <t>545068</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>602518</t>
+          <t>601628</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1058540</t>
+          <t>1053870</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1130723</t>
+          <t>1125460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>73,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>78,81%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124874</t>
+          <t>123724</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171101</t>
+          <t>171362</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159454</t>
+          <t>160344</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>218131</t>
+          <t>216904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>297404</t>
+          <t>302667</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>369587</t>
+          <t>374257</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>21,19%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P2A_R-Habitat-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39880</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31631</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49447</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>33,71%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,74%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>41,8%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>29244</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22183</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>36681</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22133</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37415</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>27,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>21,08%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>34,86%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>39880</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31215</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48273</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>33,71%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>40,81%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>58188</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80411</t>
+          <t>81421</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>26,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>36,43%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>78409</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>68842</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86658</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>66,29%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>58,2%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>73,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>75965</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>68528</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>83026</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67794</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>83076</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>72,2%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>65,14%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>78,92%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>113</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>78409</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>70016</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87074</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>66,29%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>59,19%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>73,61%</t>
+          <t>78,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>143088</t>
+          <t>142078</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165838</t>
+          <t>165311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>63,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,97%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>118289</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>105209</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>118289</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51795</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>42274</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>60960</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>30,04%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>43,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>38430</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>30537</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>46393</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>31134</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>47208</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>30,75%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,44%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>37,12%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>51795</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>42773</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>60345</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>37,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>78600</t>
+          <t>77612</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>102179</t>
+          <t>102427</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,46%</t>
+          <t>38,55%</t>
         </is>
       </c>
     </row>
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>88947</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>79782</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>98468</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>63,2%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>56,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>69,96%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>139</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>86535</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>78572</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>94428</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>77757</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>93831</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>69,25%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>62,88%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,56%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>88947</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>80397</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>97969</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>63,2%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,61%</t>
+          <t>75,09%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163528</t>
+          <t>163280</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>187107</t>
+          <t>188095</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,79%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>140742</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>124965</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>140742</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,107 +1409,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>47541</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>39194</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>55665</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>42,23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>34,82%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>49,45%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>42262</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35328</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>51099</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>34318</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>50324</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>39,19%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>32,76%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>47,38%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>47541</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>40240</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>55911</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>42,23%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>46,66%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>89802</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>78805</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>100588</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>40,74%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
           <t>35,75%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>49,67%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>89802</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>79312</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>101600</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>40,74%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>35,98%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,63%</t>
         </is>
       </c>
     </row>
@@ -1522,107 +1522,107 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>65032</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>56908</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>73379</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>57,77%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>50,55%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>65,18%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>108</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>65586</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>56749</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>72520</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>57524</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>73530</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>60,81%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>52,62%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>67,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>65032</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>56662</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>72333</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>57,77%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>53,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
+          <t>68,18%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>130618</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>119832</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>141615</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>59,26%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>54,37%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>64,25%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>130618</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>118820</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>141108</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>59,26%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>64,02%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>112573</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>177</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>107848</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>112573</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57994</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>48788</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>68320</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,95%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,09%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>43,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>55700</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>45141</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>66415</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>45122</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>66149</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>33,69%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>27,3%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,17%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>57994</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>48677</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>67939</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,95%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>99006</t>
+          <t>99996</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126188</t>
+          <t>127708</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>98952</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>88626</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>108158</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>63,05%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>56,47%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,91%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>144</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>109636</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>98921</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>120195</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>99187</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>120214</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>66,31%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>59,83%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>72,7%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>98952</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>89007</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>108269</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>63,05%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196094</t>
+          <t>194574</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>223276</t>
+          <t>222286</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,97%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>156946</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>165336</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>156946</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>197211</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>179147</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>213532</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>37,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>165636</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>148119</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>182107</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>149198</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>182885</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>32,91%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>29,43%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>36,18%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>197211</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>179464</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>214454</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>37,31%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>33,95%</t>
+          <t>29,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,57%</t>
+          <t>36,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>337770</t>
+          <t>338740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>388260</t>
+          <t>388537</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,65%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>495</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>331338</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>315017</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>349402</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>62,69%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>59,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>500</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>337723</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>321252</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>355240</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>320474</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>354161</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>67,09%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>63,82%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>70,57%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>495</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>331338</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>314095</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>349085</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>62,69%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>66,05%</t>
+          <t>70,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>643648</t>
+          <t>643371</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>694138</t>
+          <t>693168</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,35%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>67,17%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2670,72 +2670,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40360</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>32308</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>48747</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>35,88%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,72%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>43,33%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>34642</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>26680</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>43409</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>27518</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>42865</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>35,67%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>40360</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>31748</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>48999</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>35,88%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>44,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64101</t>
+          <t>63092</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>86393</t>
+          <t>86514</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,27%</t>
         </is>
       </c>
     </row>
@@ -2783,72 +2783,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72141</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>63754</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>80193</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>64,12%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>56,67%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>71,28%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>62487</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>53720</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>70449</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54264</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>69611</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>64,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>72,53%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72141</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63502</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80753</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>64,12%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123236</t>
+          <t>123115</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145528</t>
+          <t>146537</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,9%</t>
         </is>
       </c>
     </row>
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>112501</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>97129</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>112501</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3013,72 +3013,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>60402</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51690</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>71191</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>39,08%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>33,44%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>46,06%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>72</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>47166</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>39079</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>56847</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>38373</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>56435</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>36,57%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>30,3%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>44,07%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>60402</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>50866</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>70682</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>39,08%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95246</t>
+          <t>95191</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>120370</t>
+          <t>121188</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>42,45%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>94154</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83365</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>102866</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>60,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>53,94%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>66,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>81817</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>72136</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>89904</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>72548</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>90610</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>63,43%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>55,93%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>69,7%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>94154</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>83874</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>103690</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>60,92%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>56,25%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>163169</t>
+          <t>162351</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>188293</t>
+          <t>188348</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>57,55%</t>
+          <t>57,26%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,43%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>154556</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>199</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>128983</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>154556</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3356,72 +3356,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>39990</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>32464</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48879</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>34,24%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>27,8%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41,85%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>54</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>34194</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27155</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41943</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>26871</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42196</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>32,61%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>25,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>40,0%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>39990</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>32396</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>49012</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>34,24%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>40,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>63120</t>
+          <t>63671</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>85201</t>
+          <t>85062</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>38,44%</t>
+          <t>38,38%</t>
         </is>
       </c>
     </row>
@@ -3469,72 +3469,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>76794</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>67905</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84320</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>65,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>58,15%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>72,2%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>70657</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>62908</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>77696</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62655</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>77980</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>67,39%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>60,0%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>74,1%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>76794</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>67772</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>84388</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>65,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,26%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>136433</t>
+          <t>136572</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>158514</t>
+          <t>157963</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>61,56%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,27%</t>
         </is>
       </c>
     </row>
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>116784</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>104851</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>116784</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>48566</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>38851</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>59271</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>31,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,25%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>53069</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>43786</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>64264</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>43143</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>62617</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>36,35%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,99%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,02%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>48566</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>38758</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>59118</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>31,34%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>42,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>88594</t>
+          <t>88306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>116080</t>
+          <t>116072</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106375</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>95670</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116090</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>68,66%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,75%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>74,93%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>92933</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>81738</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>102216</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>83385</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>102859</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>63,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,98%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>70,01%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106375</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>95823</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>116183</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>68,66%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,99%</t>
+          <t>70,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>184863</t>
+          <t>184871</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>212349</t>
+          <t>212637</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,66%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>154941</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>191</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>146002</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>212</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>154941</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>189318</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>171369</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>208553</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>35,14%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>31,81%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>38,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>241</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>169071</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>153097</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>186219</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>151473</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>186786</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>35,45%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>39,04%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>189318</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>172497</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>208367</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>35,14%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,67%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>333254</t>
+          <t>332062</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>384731</t>
+          <t>381335</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>37,54%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>349463</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>330228</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>367412</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>64,86%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>61,29%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>68,19%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>446</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>307894</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>290746</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>323868</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>290179</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>325492</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>64,55%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>60,96%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>67,9%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>349463</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>330414</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>366284</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>64,86%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>631015</t>
+          <t>634411</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>682492</t>
+          <t>683684</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,12%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>538781</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>687</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>476965</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>538781</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4622,67 +4622,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>31745</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24868</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>40151</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>30,33%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>23,76%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>38,36%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>29617</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22618</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37716</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>22647</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>32,88%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>25,11%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>41,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>31745</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>24336</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>40883</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>30,33%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>41,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50057</t>
+          <t>49914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71730</t>
+          <t>72577</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>72929</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>64523</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>79806</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>69,67%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>61,64%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>76,24%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>60468</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52369</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>67467</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>52437</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>67438</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>67,12%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>58,13%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>74,89%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>72929</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>63791</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>80338</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>69,67%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123029</t>
+          <t>122182</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>144702</t>
+          <t>144845</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>62,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>74,37%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>104674</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90085</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>104674</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>61947</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>51695</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>71846</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>35,34%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>29,49%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>40,98%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>83</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>51320</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>43190</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>60729</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>42918</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>61587</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>33,78%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>28,43%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>39,97%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>61947</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>51717</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>72240</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>35,34%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99422</t>
+          <t>100647</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125874</t>
+          <t>126921</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,79%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>113356</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>103457</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>123608</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>64,66%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>59,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>70,51%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>162</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>100607</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>91198</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>108737</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>90340</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>109009</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>66,22%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,03%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>169</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>113356</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>103063</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>123586</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>64,66%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>59,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>201356</t>
+          <t>200309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227808</t>
+          <t>226583</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,62%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>175303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>245</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>151927</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>175303</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>45038</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35837</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>53627</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>33,9%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>26,98%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>40,37%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>34505</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>26917</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>41561</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>27474</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>42370</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>29,6%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>23,09%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>35,66%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>45038</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>36532</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>54500</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>33,9%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>27,5%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>36,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>68521</t>
+          <t>68544</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>92144</t>
+          <t>91702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,95%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>87809</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>79220</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>97010</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>66,1%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>59,63%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>73,02%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>82047</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>74991</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>89635</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>74182</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89078</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>70,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>64,34%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>76,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>87809</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>78347</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>96315</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>66,1%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>72,5%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157255</t>
+          <t>157697</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>180878</t>
+          <t>180855</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>63,05%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,52%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132847</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>116552</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>198</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132847</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>51612</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42142</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>61489</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,62%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>26,64%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>38,87%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>63702</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>53018</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>74548</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>53195</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>74535</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>38,18%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>31,78%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>44,69%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>51612</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>42236</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>61613</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>32,62%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>44,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>100302</t>
+          <t>101249</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>129361</t>
+          <t>129645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,8%</t>
+          <t>39,89%</t>
         </is>
       </c>
     </row>
@@ -5759,72 +5759,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>106596</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>96719</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>116066</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,38%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>61,13%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>73,36%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>140</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>103125</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>92279</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>113809</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>92292</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>113632</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>61,82%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>68,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>106596</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>96595</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>115972</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>67,38%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195674</t>
+          <t>195390</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>224733</t>
+          <t>223786</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,2%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,14%</t>
+          <t>68,85%</t>
         </is>
       </c>
     </row>
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158208</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>224</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166827</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>226</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158208</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>190343</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>172936</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>210538</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>33,33%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>36,87%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>266</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>179144</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>162427</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>199215</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>161254</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>195993</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>34,1%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>30,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>37,92%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>190343</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>169476</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>207926</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>33,33%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>30,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>37,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>346326</t>
+          <t>343486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>396908</t>
+          <t>397367</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,24%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>548</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>380690</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>360495</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>398097</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>63,13%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>69,72%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>524</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>346246</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>326175</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>362963</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>329397</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>364136</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>65,9%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>62,08%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>69,08%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>548</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>380690</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>363107</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>401557</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>66,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>62,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>69,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>699515</t>
+          <t>699056</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>750097</t>
+          <t>752937</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>68,67%</t>
         </is>
       </c>
     </row>
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>571033</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>525390</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>825</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>571033</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>90105</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>69813</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>101249</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>55,45%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>80,42%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>149</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>90123</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82328</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>97064</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>76,84%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>70,2%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>94665</t>
+          <t>93839</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>72433</t>
+          <t>86339</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>109469</t>
+          <t>100682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>51,59%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>184789</t>
+          <t>183944</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>158766</t>
+          <t>161254</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>201845</t>
+          <t>196116</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>74,48%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>79,41%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35801</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24657</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>56093</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>28,43%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>19,58%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>44,55%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27157</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20216</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34952</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>23,16%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,24%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>29,8%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>45747</t>
+          <t>27232</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30943</t>
+          <t>20389</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67979</t>
+          <t>34732</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>28,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>72904</t>
+          <t>63033</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>55848</t>
+          <t>50861</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>98927</t>
+          <t>85723</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>34,71%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>179765</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>164763</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>191719</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>75,78%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>69,46%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>80,82%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>215</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>140114</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>123733</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>150249</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>73,55%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>64,95%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>266</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>190549</t>
+          <t>140094</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>174801</t>
+          <t>130156</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>203275</t>
+          <t>149661</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>74,71%</t>
+          <t>75,97%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>330664</t>
+          <t>319859</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>306851</t>
+          <t>303414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>347958</t>
+          <t>335398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>74,22%</t>
+          <t>75,86%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>78,1%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -7020,72 +7020,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>57441</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>45487</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>72443</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24,22%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>19,18%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>30,54%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>65</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>50398</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>40263</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>66779</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>26,45%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>35,05%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>64486</t>
+          <t>44319</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>51760</t>
+          <t>34752</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80234</t>
+          <t>54257</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>31,46%</t>
+          <t>29,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>114884</t>
+          <t>101760</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>97590</t>
+          <t>86221</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>138697</t>
+          <t>118205</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>24,14%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>28,04%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>343</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>237206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>343</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>255035</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>445548</t>
+          <t>421619</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>154115</t>
+          <t>130479</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>141329</t>
+          <t>120291</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>168869</t>
+          <t>140452</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>77,51%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>71,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>143586</t>
+          <t>120386</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>131912</t>
+          <t>111250</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153470</t>
+          <t>129074</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>77,49%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>297701</t>
+          <t>250865</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>281989</t>
+          <t>235594</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318044</t>
+          <t>262870</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>75,06%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,66%</t>
+          <t>80,79%</t>
         </is>
       </c>
     </row>
@@ -7363,72 +7363,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>37862</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>27889</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>48050</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>22,49%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>16,57%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>28,54%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>36286</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>21532</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>49072</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>19,06%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>11,31%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>25,77%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>36664</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>31816</t>
+          <t>27976</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>53374</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>22,51%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>77986</t>
+          <t>74526</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>57643</t>
+          <t>62521</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>93698</t>
+          <t>89797</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,34%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>24,94%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>168341</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185286</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>375687</t>
+          <t>325391</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>138691</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>130451</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>146701</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>81,88%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>77,02%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>193</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>134393</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>125229</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>143317</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>80,01%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>74,56%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>85,33%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>147649</t>
+          <t>133592</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>136392</t>
+          <t>123930</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>155306</t>
+          <t>142545</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>79,93%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>75,26%</t>
+          <t>74,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>282042</t>
+          <t>272283</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>268904</t>
+          <t>260451</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>293381</t>
+          <t>283821</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,91%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,4%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,34%</t>
         </is>
       </c>
     </row>
@@ -7706,72 +7706,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>30685</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>22675</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>38925</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>18,12%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>13,39%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>22,98%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33569</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>24645</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>42733</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>19,99%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>14,67%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>25,44%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>33589</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25932</t>
+          <t>24600</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>44846</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,74%</t>
+          <t>25,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>67159</t>
+          <t>64238</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55820</t>
+          <t>52700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>80297</t>
+          <t>76070</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,09%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,6%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>169376</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>167962</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>238</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>181238</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>349201</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>539040</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>512446</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>559254</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>76,91%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79,8%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>731</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>518745</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>494793</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>542431</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,87%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,28%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>81,43%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>765</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>576450</t>
+          <t>487909</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>545068</t>
+          <t>470432</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>601628</t>
+          <t>505171</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>75,65%</t>
+          <t>77,49%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>78,96%</t>
+          <t>80,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1095195</t>
+          <t>1026950</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1053870</t>
+          <t>996381</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1125460</t>
+          <t>1055093</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>76,69%</t>
+          <t>77,18%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,79%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>79,3%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>147410</t>
+          <t>161789</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>123724</t>
+          <t>141575</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>171362</t>
+          <t>188383</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>185522</t>
+          <t>141769</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>160344</t>
+          <t>124507</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>216904</t>
+          <t>159246</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>24,35%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>19,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>332932</t>
+          <t>303558</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>302667</t>
+          <t>275415</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374257</t>
+          <t>334127</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>23,31%</t>
+          <t>22,82%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>977</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>700829</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>943</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>666155</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>977</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>761972</t>
+          <t>629678</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1428127</t>
+          <t>1330508</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
